--- a/docs/data/jp/xlsx/2326.xlsx
+++ b/docs/data/jp/xlsx/2326.xlsx
@@ -10605,7 +10605,7 @@
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Shares Of Subsidiaries Ope CF</t>
+          <t>자회사 주식 평가손</t>
         </is>
       </c>
       <c r="P146" s="22" t="n">
@@ -11750,7 +11750,7 @@
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Shares To Non Controlling Shareholders Fin CF</t>
+          <t>비지배주주로부터 주식 취득 지출</t>
         </is>
       </c>
       <c r="Q172" s="22" t="n">
@@ -11819,7 +11819,7 @@
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Deposits For Purchase Of Treasury Shares Fin CF</t>
+          <t>자기주식 취득용 예탁금 증감액(△는 증가)</t>
         </is>
       </c>
       <c r="D175" s="22" t="n">
